--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251226_201433.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251226_201433.xlsx
@@ -5016,7 +5016,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251226_201433.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251226_201433.xlsx
@@ -5624,7 +5624,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5764,7 +5764,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6302,7 +6302,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7842,7 +7842,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251226_201433.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251226_201433.xlsx
@@ -7690,7 +7690,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7842,7 +7842,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251226_201433.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251226_201433.xlsx
@@ -7690,7 +7690,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7842,7 +7842,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251226_201433.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251226_201433.xlsx
@@ -5016,7 +5016,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251226_201433.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251226_201433.xlsx
@@ -5016,7 +5016,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5624,7 +5624,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5764,7 +5764,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6302,7 +6302,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7842,7 +7842,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251226_201433.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251226_201433.xlsx
@@ -5016,7 +5016,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7842,7 +7842,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251226_201433.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251226_201433.xlsx
@@ -5016,7 +5016,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5624,7 +5624,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5764,7 +5764,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6302,7 +6302,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7842,7 +7842,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251226_201433.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251226_201433.xlsx
@@ -5016,7 +5016,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7842,7 +7842,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
